--- a/Electronics/PCBs/Motor Driver/PickAndPlace.xlsx
+++ b/Electronics/PCBs/Motor Driver/PickAndPlace.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="99">
   <si>
     <t>Designator</t>
   </si>
@@ -82,78 +82,63 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>CN-EARS</t>
-  </si>
-  <si>
-    <t>B2B-PH-K-S(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CONN-TH_B2B-PH-K-S</t>
+    <t>CN-BL</t>
+  </si>
+  <si>
+    <t>B3B-PH-K-S(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN-TH_B3B-PH-K-S</t>
+  </si>
+  <si>
+    <t>6mm</t>
+  </si>
+  <si>
+    <t>-4.8mm</t>
+  </si>
+  <si>
+    <t>8mm</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>CN-BR</t>
+  </si>
+  <si>
+    <t>-25.2mm</t>
+  </si>
+  <si>
+    <t>4mm</t>
+  </si>
+  <si>
+    <t>CN-FL</t>
+  </si>
+  <si>
+    <t>18mm</t>
+  </si>
+  <si>
+    <t>20mm</t>
+  </si>
+  <si>
+    <t>CN-FR</t>
+  </si>
+  <si>
+    <t>16mm</t>
+  </si>
+  <si>
+    <t>CN-SIGNAL</t>
+  </si>
+  <si>
+    <t>B5B-PH-K-S(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN-TH_B5B-PH-K-S-LF-SN</t>
   </si>
   <si>
     <t>45.2mm</t>
   </si>
   <si>
-    <t>-7.9mm</t>
-  </si>
-  <si>
-    <t>-8.9mm</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>CN-BL</t>
-  </si>
-  <si>
-    <t>B3B-PH-K-S(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CONN-TH_B3B-PH-K-S</t>
-  </si>
-  <si>
-    <t>6mm</t>
-  </si>
-  <si>
-    <t>-4.8mm</t>
-  </si>
-  <si>
-    <t>8mm</t>
-  </si>
-  <si>
-    <t>CN-BR</t>
-  </si>
-  <si>
-    <t>-25.2mm</t>
-  </si>
-  <si>
-    <t>4mm</t>
-  </si>
-  <si>
-    <t>CN-FL</t>
-  </si>
-  <si>
-    <t>18mm</t>
-  </si>
-  <si>
-    <t>20mm</t>
-  </si>
-  <si>
-    <t>CN-FR</t>
-  </si>
-  <si>
-    <t>16mm</t>
-  </si>
-  <si>
-    <t>CN-SIGNAL</t>
-  </si>
-  <si>
-    <t>B5B-PH-K-S(LF)(SN)</t>
-  </si>
-  <si>
-    <t>CONN-TH_B5B-PH-K-S-LF-SN</t>
-  </si>
-  <si>
     <t>-19mm</t>
   </si>
   <si>
@@ -250,28 +235,31 @@
     <t>R13</t>
   </si>
   <si>
+    <t>36mm</t>
+  </si>
+  <si>
+    <t>-5mm</t>
+  </si>
+  <si>
+    <t>-4mm</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>33.5mm</t>
+  </si>
+  <si>
+    <t>R-LS</t>
+  </si>
+  <si>
+    <t>0805W8F2003T5E</t>
+  </si>
+  <si>
+    <t>-27.5mm</t>
+  </si>
+  <si>
     <t>41mm</t>
-  </si>
-  <si>
-    <t>-9.5mm</t>
-  </si>
-  <si>
-    <t>42mm</t>
-  </si>
-  <si>
-    <t>R14</t>
-  </si>
-  <si>
-    <t>-6.5mm</t>
-  </si>
-  <si>
-    <t>R-LS</t>
-  </si>
-  <si>
-    <t>0805W8F2003T5E</t>
-  </si>
-  <si>
-    <t>-27.5mm</t>
   </si>
   <si>
     <t>200kΩ</t>
@@ -696,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -813,19 +801,19 @@
         <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="s">
         <v>21</v>
       </c>
       <c r="L3">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M3" t="s">
         <v>29</v>
@@ -839,28 +827,28 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" t="s">
-        <v>35</v>
-      </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -869,42 +857,42 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M4" t="s">
         <v>29</v>
       </c>
       <c r="N4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -913,42 +901,42 @@
         <v>21</v>
       </c>
       <c r="L5">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M5" t="s">
         <v>29</v>
       </c>
       <c r="N5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>34</v>
       </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -957,57 +945,57 @@
         <v>21</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M6" t="s">
         <v>29</v>
       </c>
       <c r="N6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>42</v>
       </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" t="s">
         <v>43</v>
       </c>
-      <c r="I7" t="s">
-        <v>37</v>
-      </c>
       <c r="J7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
       </c>
       <c r="L7">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M7" t="s">
         <v>29</v>
       </c>
       <c r="N7" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1021,34 +1009,34 @@
         <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
         <v>47</v>
       </c>
-      <c r="F8" t="s">
-        <v>26</v>
-      </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="I8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K8" t="s">
         <v>21</v>
       </c>
       <c r="L8">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="N8" t="s">
         <v>45</v>
@@ -1056,75 +1044,75 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
         <v>54</v>
       </c>
       <c r="I9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K9" t="s">
         <v>21</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M9" t="s">
         <v>22</v>
       </c>
       <c r="N9" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" t="s">
         <v>56</v>
-      </c>
-      <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10" t="s">
-        <v>59</v>
-      </c>
-      <c r="I10" t="s">
-        <v>61</v>
       </c>
       <c r="J10">
         <v>2</v>
@@ -1139,36 +1127,36 @@
         <v>22</v>
       </c>
       <c r="N10" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" t="s">
         <v>60</v>
       </c>
-      <c r="F11" t="s">
-        <v>40</v>
-      </c>
       <c r="G11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" t="s">
         <v>60</v>
       </c>
-      <c r="H11" t="s">
-        <v>40</v>
-      </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J11">
         <v>2</v>
@@ -1183,36 +1171,36 @@
         <v>22</v>
       </c>
       <c r="N11" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -1227,36 +1215,36 @@
         <v>22</v>
       </c>
       <c r="N12" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="I13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1271,36 +1259,36 @@
         <v>22</v>
       </c>
       <c r="N13" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H14" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="I14" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -1315,36 +1303,36 @@
         <v>22</v>
       </c>
       <c r="N14" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H15" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I15" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -1359,36 +1347,36 @@
         <v>22</v>
       </c>
       <c r="N15" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="G16" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H16" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="I16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -1403,36 +1391,36 @@
         <v>22</v>
       </c>
       <c r="N16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="I17" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J17">
         <v>2</v>
@@ -1447,36 +1435,36 @@
         <v>22</v>
       </c>
       <c r="N17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" t="s">
         <v>67</v>
       </c>
-      <c r="E18" t="s">
-        <v>72</v>
-      </c>
       <c r="F18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" t="s">
         <v>67</v>
       </c>
-      <c r="G18" t="s">
-        <v>72</v>
-      </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="I18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J18">
         <v>2</v>
@@ -1491,36 +1479,36 @@
         <v>22</v>
       </c>
       <c r="N18" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="G19" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H19" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="I19" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J19">
         <v>2</v>
@@ -1535,36 +1523,36 @@
         <v>22</v>
       </c>
       <c r="N19" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F20" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="G20" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H20" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="I20" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J20">
         <v>2</v>
@@ -1579,36 +1567,36 @@
         <v>22</v>
       </c>
       <c r="N20" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="I21" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -1623,80 +1611,80 @@
         <v>22</v>
       </c>
       <c r="N21" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" t="s">
         <v>78</v>
       </c>
-      <c r="B22" t="s">
+      <c r="E22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" t="s">
+        <v>78</v>
+      </c>
+      <c r="I22" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22">
+        <v>270</v>
+      </c>
+      <c r="M22" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" t="s">
         <v>57</v>
-      </c>
-      <c r="C22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G22" t="s">
-        <v>80</v>
-      </c>
-      <c r="H22" t="s">
-        <v>81</v>
-      </c>
-      <c r="I22" t="s">
-        <v>80</v>
-      </c>
-      <c r="J22">
-        <v>2</v>
-      </c>
-      <c r="K22" t="s">
-        <v>21</v>
-      </c>
-      <c r="L22">
-        <v>180</v>
-      </c>
-      <c r="M22" t="s">
-        <v>22</v>
-      </c>
-      <c r="N22" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G23" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" t="s">
         <v>82</v>
       </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" t="s">
-        <v>83</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>81</v>
-      </c>
-      <c r="I23" t="s">
-        <v>83</v>
       </c>
       <c r="J23">
         <v>2</v>
@@ -1711,7 +1699,7 @@
         <v>22</v>
       </c>
       <c r="N23" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -1722,25 +1710,25 @@
         <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" t="s">
         <v>86</v>
       </c>
-      <c r="F24" t="s">
-        <v>52</v>
-      </c>
       <c r="G24" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I24" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -1749,42 +1737,42 @@
         <v>21</v>
       </c>
       <c r="L24">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M24" t="s">
         <v>22</v>
       </c>
       <c r="N24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" t="s">
         <v>90</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>86</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>90</v>
       </c>
-      <c r="G25" t="s">
-        <v>86</v>
-      </c>
       <c r="H25" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I25" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -1799,36 +1787,36 @@
         <v>22</v>
       </c>
       <c r="N25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" t="s">
         <v>93</v>
       </c>
-      <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>58</v>
-      </c>
       <c r="D26" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" t="s">
         <v>90</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
+        <v>47</v>
+      </c>
+      <c r="G26" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" t="s">
         <v>94</v>
       </c>
-      <c r="F26" t="s">
+      <c r="I26" t="s">
         <v>90</v>
-      </c>
-      <c r="G26" t="s">
-        <v>94</v>
-      </c>
-      <c r="H26" t="s">
-        <v>91</v>
-      </c>
-      <c r="I26" t="s">
-        <v>94</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -1843,95 +1831,51 @@
         <v>22</v>
       </c>
       <c r="N26" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" t="s">
+        <v>97</v>
+      </c>
+      <c r="I27" t="s">
+        <v>98</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27">
+        <v>270</v>
+      </c>
+      <c r="M27" t="s">
+        <v>22</v>
+      </c>
+      <c r="N27" t="s">
         <v>95</v>
-      </c>
-      <c r="B27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27" t="s">
-        <v>52</v>
-      </c>
-      <c r="G27" t="s">
-        <v>94</v>
-      </c>
-      <c r="H27" t="s">
-        <v>98</v>
-      </c>
-      <c r="I27" t="s">
-        <v>94</v>
-      </c>
-      <c r="J27">
-        <v>2</v>
-      </c>
-      <c r="K27" t="s">
-        <v>21</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="s">
-        <v>22</v>
-      </c>
-      <c r="N27" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>100</v>
-      </c>
-      <c r="B28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" t="s">
-        <v>101</v>
-      </c>
-      <c r="E28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" t="s">
-        <v>101</v>
-      </c>
-      <c r="G28" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" t="s">
-        <v>101</v>
-      </c>
-      <c r="I28" t="s">
-        <v>102</v>
-      </c>
-      <c r="J28">
-        <v>2</v>
-      </c>
-      <c r="K28" t="s">
-        <v>21</v>
-      </c>
-      <c r="L28">
-        <v>270</v>
-      </c>
-      <c r="M28" t="s">
-        <v>22</v>
-      </c>
-      <c r="N28" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>
